--- a/inst/examples/onco/spec/report.xlsx
+++ b/inst/examples/onco/spec/report.xlsx
@@ -914,7 +914,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -1123,6 +1123,15 @@
     <t xml:space="preserve">Treatment-Emergent Adverse Events by System Organ Class and Preferred Term</t>
   </si>
   <si>
+    <t xml:space="preserve">T-14-3-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 14.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overview of Treatment-Emergent Adverse Events</t>
+  </si>
+  <si>
     <t xml:space="preserve">SD: standard deviation; ECOG: Eastern Cooperative Oncology Group.</t>
   </si>
   <si>
@@ -1136,6 +1145,12 @@
   </si>
   <si>
     <t xml:space="preserve">Treatment-emergent: onset from the first dose to 30 days after the last dose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A subject is counted once in each row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grades by CTCAE; treatment-related: related to the study drug, investigator assessment.</t>
   </si>
   <si>
     <t xml:space="preserve">name</t>
@@ -1905,6 +1920,45 @@
       </c>
       <c r="E10"/>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1942,7 +1996,7 @@
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
@@ -1955,7 +2009,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1968,7 +2022,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -1981,7 +2035,7 @@
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -1994,10 +2048,49 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2016,7 +2109,7 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -2044,7 +2137,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
